--- a/artifacts/关键标准答案.xlsx
+++ b/artifacts/关键标准答案.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="交付物答案清单" sheetId="1" r:id="R2ea00cf8b0d04551"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定字段答案" sheetId="2" r:id="R17a73afb2c2a469b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定集合答案" sheetId="3" r:id="R95173a7550ab4185"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定数值答案" sheetId="4" r:id="R36f402db30514c30"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="允许变体答案" sheetId="5" r:id="Ra0aee19a6e3f46ac"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="交付物答案清单" sheetId="1" r:id="R15701fb792b844d7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定字段答案" sheetId="2" r:id="Ra553b7b1f88e454d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定集合答案" sheetId="3" r:id="R66ee4ef543d64e10"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定数值答案" sheetId="4" r:id="R80b1caa33f614698"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="允许变体答案" sheetId="5" r:id="R71c156444c864e14"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -819,10 +819,10 @@
     </x:row>
     <x:row r="6" ht="33" customHeight="1">
       <x:c r="A6" s="5" t="str">
-        <x:v>上下文关闭时机</x:v>
+        <x:v>状态隔离方式</x:v>
       </x:c>
       <x:c r="B6" s="5" t="str">
-        <x:v>可在每项场景结束后关闭，也可用测试钩子关闭</x:v>
+        <x:v>可用独立context、独立page或显式清理存储</x:v>
       </x:c>
       <x:c r="C6" s="5" t="str">
         <x:v>场景之间不共享localStorage</x:v>
